--- a/package-output-map.xlsx
+++ b/package-output-map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/floswald/git/JPEtemplate/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linus/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067DD2C7-24FE-2447-A5A8-8F6542C7C06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4EA7CC-53C9-904B-8410-8ABD14BA1F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="21900" windowHeight="12060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16880" yWindow="600" windowWidth="11920" windowHeight="14240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="200">
   <si>
     <t>Data Preparation Program</t>
   </si>
@@ -46,13 +46,592 @@
   </si>
   <si>
     <t>In-text numbers</t>
+  </si>
+  <si>
+    <t>Table 5</t>
+  </si>
+  <si>
+    <t>Baseline Specification/Code/Calibration.m</t>
+  </si>
+  <si>
+    <t>427-429</t>
+  </si>
+  <si>
+    <t>Table 6</t>
+  </si>
+  <si>
+    <t>Baseline Specification/Code/MWResults/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>496-509</t>
+  </si>
+  <si>
+    <t>Table F1</t>
+  </si>
+  <si>
+    <t>511-526</t>
+  </si>
+  <si>
+    <t>Table F2</t>
+  </si>
+  <si>
+    <t>528-542</t>
+  </si>
+  <si>
+    <t>Sensitivity Specifications/Sensitivity (i) - 1+Only/Code/Calibration.m</t>
+  </si>
+  <si>
+    <t>421-425</t>
+  </si>
+  <si>
+    <t>Table G1 Column (Ii)</t>
+  </si>
+  <si>
+    <t>Sensitivity Specifications/Sensitivity (ii) - GM6 &amp; 1+/Code/Calibration.m</t>
+  </si>
+  <si>
+    <t>Table G1 Column (iii)</t>
+  </si>
+  <si>
+    <t>Sensitivity Specifications/Sensitivity (iii) - SelfEmployment, 1+ Only/Code/Calibration.m</t>
+  </si>
+  <si>
+    <t>424-428</t>
+  </si>
+  <si>
+    <t>Table G1 Column (i)</t>
+  </si>
+  <si>
+    <t>Table G1 Column (iv)</t>
+  </si>
+  <si>
+    <t>Table G1 Column (v)</t>
+  </si>
+  <si>
+    <t>Table G1 Column (vii)</t>
+  </si>
+  <si>
+    <t>Sensitivity Specifications/Sensitivity (iv) - SelfEmployment, GMR6 &amp; 1+/Code/Calibration.m</t>
+  </si>
+  <si>
+    <t>Sensitivity Specifications/Sensitivity (v) - Hours Calibration/Code/Calibration.m</t>
+  </si>
+  <si>
+    <t>425-429</t>
+  </si>
+  <si>
+    <t>Table G1 Column (vi)</t>
+  </si>
+  <si>
+    <t>Sensitivity Specifications/Sensitivity (vi) - Kaitz Calibration/Code/Calibration.m</t>
+  </si>
+  <si>
+    <t>422-427</t>
+  </si>
+  <si>
+    <t>Sensitivity Specifications/Sensitivity (vii) - Mean Ratio Calibration/Code/Calibration.m</t>
+  </si>
+  <si>
+    <t>Table H1</t>
+  </si>
+  <si>
+    <t>Unemployment Specification/Code/Calibration.m</t>
+  </si>
+  <si>
+    <t>439-443</t>
+  </si>
+  <si>
+    <t>410-421</t>
+  </si>
+  <si>
+    <t>Table H2 Upper panel</t>
+  </si>
+  <si>
+    <t>Table H2 CSV file (lower panel)</t>
+  </si>
+  <si>
+    <t>Unemployment Specification/Code/MWResults/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>383-407</t>
+  </si>
+  <si>
+    <t>Table H2 PDF file (lower panel)</t>
+  </si>
+  <si>
+    <t>R Simulation Figures/Code/TableH2.R</t>
+  </si>
+  <si>
+    <t>143-157</t>
+  </si>
+  <si>
+    <t>Table I1</t>
+  </si>
+  <si>
+    <t>Unproductive Managers Specification/Code/Calibration.m</t>
+  </si>
+  <si>
+    <t>140-143</t>
+  </si>
+  <si>
+    <t>121-131</t>
+  </si>
+  <si>
+    <t>Figure 3 Panel A</t>
+  </si>
+  <si>
+    <t>Figure 3 Panel B</t>
+  </si>
+  <si>
+    <t>108-118</t>
+  </si>
+  <si>
+    <t>Figure 4 Panel A</t>
+  </si>
+  <si>
+    <t>Baseline Specification/Code/CR-HFigures/CostMinimizationMW_h.m</t>
+  </si>
+  <si>
+    <t>91-101</t>
+  </si>
+  <si>
+    <t>Figure 4 Panel B</t>
+  </si>
+  <si>
+    <t>92-102</t>
+  </si>
+  <si>
+    <t>Baseline Specification/Code/CR-HFigures/CostMinimizationMW_c.m</t>
+  </si>
+  <si>
+    <t>Baseline Specification/Code/CR-HFigures/CostMinimizationMW.m</t>
+  </si>
+  <si>
+    <t>Baseline Specification/Code/CR-HFigures/CostMinimizationMW_A.m</t>
+  </si>
+  <si>
+    <t>Figure 4 Panel C</t>
+  </si>
+  <si>
+    <t>Figure 4 Panel D</t>
+  </si>
+  <si>
+    <t>Baseline Specification/Code/CR-HFigures/CostMinimizationMW_lambda.m</t>
+  </si>
+  <si>
+    <t>Figure 5 Panel A</t>
+  </si>
+  <si>
+    <t>Baseline Specification/Code/CR-HFigures/CostMinimizationMW_mw.m</t>
+  </si>
+  <si>
+    <t>90-100</t>
+  </si>
+  <si>
+    <t>Figure 5 Panel B</t>
+  </si>
+  <si>
+    <t>103-113</t>
+  </si>
+  <si>
+    <t>Figure 6 CSV file</t>
+  </si>
+  <si>
+    <t>447-475</t>
+  </si>
+  <si>
+    <t>Figure 6 PDF file (legend)</t>
+  </si>
+  <si>
+    <t>R Simulation Figures/Code/Figure_6_legFigG1.R</t>
+  </si>
+  <si>
+    <t>135-140</t>
+  </si>
+  <si>
+    <t>Figure 6 PDF file (figure)</t>
+  </si>
+  <si>
+    <t>151-156</t>
+  </si>
+  <si>
+    <t>Baseline Specification/Code/Decomposition/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>133-146</t>
+  </si>
+  <si>
+    <t>Figure 7 CSV file</t>
+  </si>
+  <si>
+    <t>Figure 7 PDF file</t>
+  </si>
+  <si>
+    <t>R Simulation Figures/Code/Figure_7.R</t>
+  </si>
+  <si>
+    <t>88-108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure 8 </t>
+  </si>
+  <si>
+    <t>478-487</t>
+  </si>
+  <si>
+    <t>Baseline Specification/Code/MWResults/MWResults_Technology_Output32/H_Small/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>327-336</t>
+  </si>
+  <si>
+    <t>Baseline Specification/Code/MWResults/MWResults_Technology_Output32/C_Small/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>328-337</t>
+  </si>
+  <si>
+    <t>Baseline Specification/Code/MWResults/MWResults_Technology_Output32/Lambda_Large/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>Baseline Specification/Code/MWResults/MWResults_Technology_Output32/A_Large/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>R Simulation Figures/Code/Figure_8.R</t>
+  </si>
+  <si>
+    <t>149-203</t>
+  </si>
+  <si>
+    <t>Figure 8</t>
+  </si>
+  <si>
+    <t>Figure 8 (PDF files)</t>
+  </si>
+  <si>
+    <t>Figure 8 (CSV file)</t>
+  </si>
+  <si>
+    <t>Figure A2</t>
+  </si>
+  <si>
+    <t>R Figures A2-A3/Code/Graphs_UNCERTAINTY_Bloom_v1.R</t>
+  </si>
+  <si>
+    <t>Figure A3</t>
+  </si>
+  <si>
+    <t>R Figures A2-A3/Code/Graphs_Kaitz_v1.R</t>
+  </si>
+  <si>
+    <t>Figure F1 Panel A</t>
+  </si>
+  <si>
+    <t>Baseline Specification/Code/AlphaFigures/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>123-138</t>
+  </si>
+  <si>
+    <t>Figure F1 Panel B</t>
+  </si>
+  <si>
+    <t>Figure F1 Panel C</t>
+  </si>
+  <si>
+    <t>Figure F1 Panel D</t>
+  </si>
+  <si>
+    <t>140-159</t>
+  </si>
+  <si>
+    <t>161-176</t>
+  </si>
+  <si>
+    <t>178-197</t>
+  </si>
+  <si>
+    <t>Figure F2 Panel A</t>
+  </si>
+  <si>
+    <t>Figure F2 Panel B</t>
+  </si>
+  <si>
+    <t>Baseline Specification/Code/MWResults/MWResults_Technology_Output64/H_Small/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>Baseline Specification/Code/MWResults/MWResults_Technology_Output64/C_Small/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>Baseline Specification/Code/MWResults/MWResults_Technology_Output64/Lambda_Large/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>Baseline Specification/Code/MWResults/MWResults_Technology_Output64/A_Large/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>Figure F2 Panel C</t>
+  </si>
+  <si>
+    <t>Baseline Specification/Code/MWResults/MWResults_Technology_Output96/H_Small/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>Baseline Specification/Code/MWResults/MWResults_Technology_Output96/C_Small/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>Baseline Specification/Code/MWResults/MWResults_Technology_Output96/Lambda_Large/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>R Simulation Figures/Code/Figure_F2.R</t>
+  </si>
+  <si>
+    <t>Baseline Specification/Code/MWResults/MWResults_Technology_Output96/A_Large/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>Figure F2</t>
+  </si>
+  <si>
+    <t>111-184</t>
+  </si>
+  <si>
+    <t>Figure G1 Panel (i)</t>
+  </si>
+  <si>
+    <t>Sensitivity Specifications/Sensitivity (i) - 1+Only/Code/MWResults/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>445-473</t>
+  </si>
+  <si>
+    <t>Figure G1 Panel (ii)</t>
+  </si>
+  <si>
+    <t>Sensitivity Specifications/Sensitivity (ii) - GM6 &amp;1+/Code/MWResults/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>Figure G1 Panel (iii)</t>
+  </si>
+  <si>
+    <t>Sensitivity Specifications/Sensitivity (iii) - SelfEmployment, 1+Only/Code/MWResults/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>454-482</t>
+  </si>
+  <si>
+    <t>Figure G1 Panel (iv)</t>
+  </si>
+  <si>
+    <t>Sensitivity Specifications/Sensitivity (iv) - SelfEmployment,GMR6 &amp; 1+/Code/MWResults/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>Sensitivity Specifications/Sensitivity (v) - HoursCalibration/Code/MWResults/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>Figure G1 Panel (v)</t>
+  </si>
+  <si>
+    <t>Sensitivity Specifications/Sensitivity (vi) - KaitzCalibration/Code/MWResults/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>Figure G1 Panel (vi)</t>
+  </si>
+  <si>
+    <t>Figure G1 Panel (vii)</t>
+  </si>
+  <si>
+    <t>Sensitivity Specifications/Sensitivity (vii) - Mean RatioCalibration/Code/MWResults/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>Figure G1 PDF files (figures)</t>
+  </si>
+  <si>
+    <t>R Simulation Figures/Code/Figure_G1.R</t>
+  </si>
+  <si>
+    <t>114-147</t>
+  </si>
+  <si>
+    <t>Figure G1 PDF files (legend)</t>
+  </si>
+  <si>
+    <t>142-147</t>
+  </si>
+  <si>
+    <t>Figure I1 Panel A</t>
+  </si>
+  <si>
+    <t>Unproductive Managers Specification/Code/MWResults/ProfitMaximizationMW_GE.m</t>
+  </si>
+  <si>
+    <t>96-109</t>
+  </si>
+  <si>
+    <t>Figure I1 Panel B</t>
+  </si>
+  <si>
+    <t>Figure I1 PDF files</t>
+  </si>
+  <si>
+    <t>R Simulation Figures/Code/Figure_I1.R</t>
+  </si>
+  <si>
+    <t>152-183</t>
+  </si>
+  <si>
+    <t>Figure 1A</t>
+  </si>
+  <si>
+    <t>Figure 1B</t>
+  </si>
+  <si>
+    <t>Figure 1C</t>
+  </si>
+  <si>
+    <t>Figure 2A</t>
+  </si>
+  <si>
+    <t>Figure 2B</t>
+  </si>
+  <si>
+    <t>Figure 2C</t>
+  </si>
+  <si>
+    <t>Figure 2D</t>
+  </si>
+  <si>
+    <t>Table 1</t>
+  </si>
+  <si>
+    <t>Table 2</t>
+  </si>
+  <si>
+    <t>Table 3</t>
+  </si>
+  <si>
+    <t>Table 4</t>
+  </si>
+  <si>
+    <t>Table 5 (Data column)</t>
+  </si>
+  <si>
+    <t>Table B1</t>
+  </si>
+  <si>
+    <t>Table B2</t>
+  </si>
+  <si>
+    <t>Table B3</t>
+  </si>
+  <si>
+    <t>Table B4</t>
+  </si>
+  <si>
+    <t>Table B5</t>
+  </si>
+  <si>
+    <t>Table B6</t>
+  </si>
+  <si>
+    <t>Table C1</t>
+  </si>
+  <si>
+    <t>Table C2</t>
+  </si>
+  <si>
+    <t>Table C3</t>
+  </si>
+  <si>
+    <t>Table C4</t>
+  </si>
+  <si>
+    <t>Tables D1-D4</t>
+  </si>
+  <si>
+    <t>Tables D5-D8</t>
+  </si>
+  <si>
+    <t>Tables D9-D11</t>
+  </si>
+  <si>
+    <t>Table G1 (Panel A, Share of 0-layer firms; columns iii-iv)</t>
+  </si>
+  <si>
+    <t>code/Programs/6_STATA_ANALYSES/02_build_figure1_minimum_wage_paths.do</t>
+  </si>
+  <si>
+    <t>code/Programs/6_STATA_ANALYSES/01_build_descriptive_tables.do</t>
+  </si>
+  <si>
+    <t>code/Programs/6_STATA_ANALYSES/03_build_figure2_labor_cost_distributions.do</t>
+  </si>
+  <si>
+    <t>code/Programs/6_STATA_ANALYSES/00_run_regression_analysis.do -&gt; 10_run_dd_ols.do + 11_run_ddd_ols.do -&gt; functions/fn_export_regression_tables.do</t>
+  </si>
+  <si>
+    <t>code/Programs/5_STATA_FINAL_DATA_CONSTRUCTION/00_build_final_analysis_data.do -&gt; functions/fn_compute_calibration_moments.do</t>
+  </si>
+  <si>
+    <t>code/Programs/6_STATA_ANALYSES/04_prepare_table_b1_sample_inputs.do -&gt; 05_build_table_b1_sample_construction.do</t>
+  </si>
+  <si>
+    <t>code/Programs/6_STATA_ANALYSES/00_run_regression_analysis.do -&gt; 10_run_dd_ols.do + 11_run_ddd_ols.do</t>
+  </si>
+  <si>
+    <t>code/Programs/6_STATA_ANALYSES/00_run_regression_analysis.do -&gt; 12_run_dd_iv.do + 13_run_ddd_iv.do</t>
+  </si>
+  <si>
+    <t>code/Programs/6_STATA_ANALYSES/00_run_regression_analysis.do -&gt; 10_run_dd_ols.do + 11_run_ddd_ols.do [drop GMR5]</t>
+  </si>
+  <si>
+    <t>code/Programs/6_STATA_ANALYSES/00_run_regression_analysis.do -&gt; 10_run_dd_ols.do + 11_run_ddd_ols.do [2483 subsample]</t>
+  </si>
+  <si>
+    <t>code/Programs/7_SAS_APPENDIX_G/01_compute_table_g1_zero_layer_moment.sas</t>
+  </si>
+  <si>
+    <t>Public or Private</t>
+  </si>
+  <si>
+    <t>Public</t>
+  </si>
+  <si>
+    <t>Private</t>
+  </si>
+  <si>
+    <t>yes, with diverging values</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Figure6.csv</t>
+  </si>
+  <si>
+    <t>Figure7.csv</t>
+  </si>
+  <si>
+    <t>Figure8.csv</t>
+  </si>
+  <si>
+    <t>FigureF1.csv</t>
+  </si>
+  <si>
+    <t>FigureF2.csv</t>
+  </si>
+  <si>
+    <t>FigureF2_96.csv</t>
+  </si>
+  <si>
+    <t>FigureF2_64.csv</t>
+  </si>
+  <si>
+    <t>Baseline Specification</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -67,6 +646,30 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -89,7 +692,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -100,6 +703,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,12 +1042,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:E118"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.5" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
@@ -449,7 +1058,7 @@
     <col min="13" max="13" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -460,23 +1069,84 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C8" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
@@ -489,22 +1159,1419 @@
       <c r="D10" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+      <c r="E10" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E11" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E12" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E13" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E14" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E27" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E28" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E29" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E30" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E31" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E32" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E33" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E34" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E35" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E36" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E37" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E38" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E39" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E40" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E41" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E42" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E43" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E44" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E45" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="4">
+        <v>37</v>
+      </c>
+      <c r="E46" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="4">
+        <v>86</v>
+      </c>
+      <c r="E47" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E48" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E49" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E50" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E51" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E52" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E53" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E54" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E55" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E56" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" s="4">
+        <v>490</v>
+      </c>
+      <c r="E57" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E58" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E59" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E60" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E61" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="4">
+        <v>493</v>
+      </c>
+      <c r="E62" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E63" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E64" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E65" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E66" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E67" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E68" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E69" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E70" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E71" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E72" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E73" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E74" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E75" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E76" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E77" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E78" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E79" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C80" s="4"/>
+      <c r="E80" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C81" s="4"/>
+      <c r="E81" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C82" s="4"/>
+      <c r="E82" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C83" s="4"/>
+      <c r="E83" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C84" s="4"/>
+      <c r="E84" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C85" s="4"/>
+      <c r="E85" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C86" s="4"/>
+      <c r="E86" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C87" s="4"/>
+      <c r="E87" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C88" s="4"/>
+      <c r="E88" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C89" s="4"/>
+      <c r="E89" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C90" s="4"/>
+      <c r="E90" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C91" s="4"/>
+      <c r="E91" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C92" s="4"/>
+      <c r="E92" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C93" s="4"/>
+      <c r="E93" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C94" s="4"/>
+      <c r="E94" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C95" s="4"/>
+      <c r="E95" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C96" s="4"/>
+      <c r="E96" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C97" s="4"/>
+      <c r="E97" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C98" s="4"/>
+      <c r="E98" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C99" s="4"/>
+      <c r="E99" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C100" s="4"/>
+      <c r="E100" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C101" s="4"/>
+      <c r="E101" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C102" s="4"/>
+      <c r="E102" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C103" s="4"/>
+      <c r="E103" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C104" s="4"/>
+      <c r="E104" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C105" s="4"/>
+      <c r="E105" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106" s="4"/>
+      <c r="B106" s="4"/>
+      <c r="C106" s="4"/>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107" s="4"/>
+      <c r="B107" s="4"/>
+      <c r="C107" s="4"/>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108" s="4"/>
+      <c r="B108" s="4"/>
+      <c r="C108" s="4"/>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A109" s="4"/>
+      <c r="B109" s="4"/>
+      <c r="C109" s="4"/>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110" s="4"/>
+      <c r="B110" s="4"/>
+      <c r="C110" s="4"/>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A111" s="4"/>
+      <c r="B111" s="4"/>
+      <c r="C111" s="4"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112" s="4"/>
+      <c r="B112" s="4"/>
+      <c r="C112" s="4"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A113" s="4"/>
+      <c r="B113" s="4"/>
+      <c r="C113" s="4"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A114" s="4"/>
+      <c r="B114" s="4"/>
+      <c r="C114" s="4"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A115" s="4"/>
+      <c r="B115" s="4"/>
+      <c r="C115" s="4"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A116" s="4"/>
+      <c r="B116" s="4"/>
+      <c r="C116" s="4"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A118" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B118" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C118" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D118" s="2" t="s">
         <v>2</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
